--- a/events/Prague_2013_WCH/Prague_2013_WCH_start.xlsx
+++ b/events/Prague_2013_WCH/Prague_2013_WCH_start.xlsx
@@ -12931,7 +12931,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="J332" t="n">
@@ -44183,11 +44183,6 @@
       <c r="K758" t="n">
         <v>757</v>
       </c>
-      <c r="R758" t="inlineStr">
-        <is>
-          <t>Forerunner Team 1</t>
-        </is>
-      </c>
     </row>
     <row r="759">
       <c r="B759" t="inlineStr">
@@ -44231,11 +44226,6 @@
       <c r="K759" t="n">
         <v>758</v>
       </c>
-      <c r="R759" t="inlineStr">
-        <is>
-          <t>Forerunner Team 2</t>
-        </is>
-      </c>
     </row>
     <row r="760">
       <c r="B760" t="inlineStr">
@@ -44279,11 +44269,6 @@
       <c r="K760" t="n">
         <v>759</v>
       </c>
-      <c r="R760" t="inlineStr">
-        <is>
-          <t>Forerunner Team 3</t>
-        </is>
-      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -53126,11 +53111,6 @@
       <c r="K884" t="n">
         <v>883</v>
       </c>
-      <c r="R884" t="inlineStr">
-        <is>
-          <t>Forerunner Team 4</t>
-        </is>
-      </c>
     </row>
     <row r="885">
       <c r="B885" t="inlineStr">
@@ -53173,11 +53153,6 @@
       </c>
       <c r="K885" t="n">
         <v>884</v>
-      </c>
-      <c r="R885" t="inlineStr">
-        <is>
-          <t>Forerunner Team 5</t>
-        </is>
       </c>
     </row>
     <row r="886">

--- a/events/Prague_2013_WCH/Prague_2013_WCH_start.xlsx
+++ b/events/Prague_2013_WCH/Prague_2013_WCH_start.xlsx
@@ -13423,7 +13423,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J341" t="n">

--- a/events/Prague_2013_WCH/Prague_2013_WCH_start.xlsx
+++ b/events/Prague_2013_WCH/Prague_2013_WCH_start.xlsx
@@ -13437,6 +13437,11 @@
           <t>MERJAN Richard Rashid</t>
         </is>
       </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -19660,6 +19665,11 @@
       <c r="R341" t="inlineStr">
         <is>
           <t>MERJAN Richard Rashid</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>45918</t>
         </is>
       </c>
     </row>
